--- a/CROX.xlsx
+++ b/CROX.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75C8D0D3-F337-4895-B7E4-7E39F4AF4177}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16A29BFE-70C8-4CD1-8E75-9F98B17ED35B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{CE56C274-430F-49C4-B695-C61D5C0F48E5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{CE56C274-430F-49C4-B695-C61D5C0F48E5}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -4826,6 +4826,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4843,9 +4846,6 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -5470,7 +5470,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="77">
-        <v>102.6</v>
+        <v>136.34</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -5480,7 +5480,7 @@
       <c r="H3" s="77">
         <v>49.689647999999998</v>
       </c>
-      <c r="I3" s="105" t="s">
+      <c r="I3" s="99" t="s">
         <v>1385</v>
       </c>
     </row>
@@ -5493,7 +5493,7 @@
       </c>
       <c r="H4" s="77">
         <f>H3*H2</f>
-        <v>5098.1578847999999</v>
+        <v>6774.6866083200002</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -5506,7 +5506,7 @@
       <c r="H5" s="77">
         <v>130.881</v>
       </c>
-      <c r="I5" s="105" t="s">
+      <c r="I5" s="99" t="s">
         <v>1385</v>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
         <f>1330.271+5.55</f>
         <v>1335.8209999999999</v>
       </c>
-      <c r="I6" s="105" t="s">
+      <c r="I6" s="99" t="s">
         <v>1385</v>
       </c>
     </row>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="H7" s="77">
         <f>H4+H6-H5</f>
-        <v>6303.0978847999995</v>
+        <v>7979.6266083199998</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -5771,16 +5771,16 @@
       <c r="N2" s="78" t="s">
         <v>335</v>
       </c>
-      <c r="O2" s="105" t="s">
+      <c r="O2" s="99" t="s">
         <v>1385</v>
       </c>
-      <c r="P2" s="105" t="s">
+      <c r="P2" s="99" t="s">
         <v>1386</v>
       </c>
-      <c r="Q2" s="105" t="s">
+      <c r="Q2" s="99" t="s">
         <v>1387</v>
       </c>
-      <c r="R2" s="105" t="s">
+      <c r="R2" s="99" t="s">
         <v>1388</v>
       </c>
       <c r="S2" s="78"/>
@@ -27867,7 +27867,7 @@
       </c>
       <c r="F36" s="5">
         <f>+Main!H4</f>
-        <v>5098.1578847999999</v>
+        <v>6774.6866083200002</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.2">
@@ -27876,7 +27876,7 @@
       </c>
       <c r="F37" s="5">
         <f>F35+F36</f>
-        <v>6433.9788847999998</v>
+        <v>8110.5076083200001</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.2">
@@ -27899,7 +27899,7 @@
       <c r="E41" s="8"/>
       <c r="F41" s="74">
         <f>+((F35/F37)*F32*(1-F39))+(F36/F37)*F22</f>
-        <v>0.11589228102815466</v>
+        <v>0.12035078302102463</v>
       </c>
       <c r="H41" s="54" t="s">
         <v>254</v>
@@ -27971,14 +27971,14 @@
       </c>
       <c r="J3" s="20">
         <f>+Main!H2</f>
-        <v>102.6</v>
+        <v>136.34</v>
       </c>
       <c r="L3" s="5" t="s">
         <v>257</v>
       </c>
       <c r="O3" s="20">
         <f>+J3</f>
-        <v>102.6</v>
+        <v>136.34</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.2">
@@ -27987,14 +27987,14 @@
       </c>
       <c r="E4" s="21">
         <f ca="1">+TODAY()</f>
-        <v>46143</v>
+        <v>46226</v>
       </c>
       <c r="G4" s="5" t="s">
         <v>259</v>
       </c>
       <c r="J4" s="22">
         <f ca="1">V62</f>
-        <v>150.73682790166654</v>
+        <v>149.81272597413047</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>260</v>
@@ -28016,7 +28016,7 @@
       </c>
       <c r="J5" s="24">
         <f ca="1">J4/J3-1</f>
-        <v>0.46916986258934257</v>
+        <v>9.8817118777544843E-2</v>
       </c>
       <c r="L5" s="5" t="s">
         <v>262</v>
@@ -29605,43 +29605,43 @@
       <c r="L52" s="50"/>
       <c r="M52" s="50">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>225.82387364210103</v>
+        <v>370.34250261480412</v>
       </c>
       <c r="N52" s="50">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>631.21214157864483</v>
+        <v>617.01877721719779</v>
       </c>
       <c r="O52" s="50">
         <f t="shared" ref="O52:U52" ca="1" si="21">O51/(1+$E$18)^O53</f>
-        <v>592.38344519361385</v>
+        <v>579.06317847901244</v>
       </c>
       <c r="P52" s="50">
         <f t="shared" ca="1" si="21"/>
-        <v>555.37657757645627</v>
+        <v>542.88844307441423</v>
       </c>
       <c r="Q52" s="50">
         <f t="shared" ca="1" si="21"/>
-        <v>520.1714053531648</v>
+        <v>508.47489034615177</v>
       </c>
       <c r="R52" s="50">
         <f t="shared" ca="1" si="21"/>
-        <v>486.73905384195007</v>
+        <v>475.79429488524357</v>
       </c>
       <c r="S52" s="50">
         <f t="shared" ca="1" si="21"/>
-        <v>455.04319282569793</v>
+        <v>444.81114339170171</v>
       </c>
       <c r="T52" s="50">
         <f t="shared" ca="1" si="21"/>
-        <v>425.04122793376501</v>
+        <v>415.4837992670524</v>
       </c>
       <c r="U52" s="50">
         <f t="shared" ca="1" si="21"/>
-        <v>396.68539634496364</v>
+        <v>387.76557367946828</v>
       </c>
       <c r="V52" s="51">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>369.92376718735005</v>
+        <v>361.6057034686803</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -29650,43 +29650,43 @@
       </c>
       <c r="M53" s="52">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.33611111111111114</v>
+        <v>0.56388888888888888</v>
       </c>
       <c r="N53" s="52">
         <f ca="1">M53+1</f>
-        <v>1.3361111111111112</v>
+        <v>1.5638888888888889</v>
       </c>
       <c r="O53" s="52">
         <f ca="1">N53+1</f>
-        <v>2.3361111111111112</v>
+        <v>2.5638888888888891</v>
       </c>
       <c r="P53" s="52">
         <f t="shared" ref="P53:V53" ca="1" si="22">O53+1</f>
-        <v>3.3361111111111112</v>
+        <v>3.5638888888888891</v>
       </c>
       <c r="Q53" s="52">
         <f t="shared" ca="1" si="22"/>
-        <v>4.3361111111111112</v>
+        <v>4.5638888888888891</v>
       </c>
       <c r="R53" s="52">
         <f t="shared" ca="1" si="22"/>
-        <v>5.3361111111111112</v>
+        <v>5.5638888888888891</v>
       </c>
       <c r="S53" s="52">
         <f t="shared" ca="1" si="22"/>
-        <v>6.3361111111111112</v>
+        <v>6.5638888888888891</v>
       </c>
       <c r="T53" s="52">
         <f t="shared" ca="1" si="22"/>
-        <v>7.3361111111111112</v>
+        <v>7.5638888888888891</v>
       </c>
       <c r="U53" s="52">
         <f t="shared" ca="1" si="22"/>
-        <v>8.3361111111111121</v>
+        <v>8.56388888888889</v>
       </c>
       <c r="V53" s="52">
         <f t="shared" ca="1" si="22"/>
-        <v>9.3361111111111121</v>
+        <v>9.56388888888889</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -29699,7 +29699,7 @@
       <c r="Q54" s="53"/>
       <c r="V54" s="32">
         <f ca="1">SUM(M52:V52)</f>
-        <v>4658.4000814777073</v>
+        <v>4703.2483064237267</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -29743,7 +29743,7 @@
       <c r="U56" s="55"/>
       <c r="V56" s="56">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>4036.5998375926829</v>
+        <v>3945.8333131512754</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -29771,7 +29771,7 @@
       <c r="U57" s="57"/>
       <c r="V57" s="58">
         <f ca="1">V54+V56</f>
-        <v>8694.9999190703893</v>
+        <v>8649.0816195750012</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -29825,7 +29825,7 @@
       <c r="Q60" s="53"/>
       <c r="V60" s="59">
         <f ca="1">V57+V58-V59</f>
-        <v>7490.0599190703888</v>
+        <v>7444.1416195750007</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -29862,7 +29862,7 @@
       </c>
       <c r="V62" s="59">
         <f ca="1">V60/V61</f>
-        <v>150.73682790166654</v>
+        <v>149.81272597413047</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -29895,35 +29895,35 @@
     </row>
     <row r="68" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B68" s="60"/>
-      <c r="C68" s="99" t="s">
+      <c r="C68" s="100" t="s">
         <v>274</v>
       </c>
-      <c r="D68" s="99"/>
-      <c r="E68" s="99"/>
-      <c r="F68" s="99"/>
-      <c r="G68" s="99"/>
-      <c r="H68" s="99"/>
-      <c r="I68" s="99"/>
-      <c r="J68" s="100"/>
+      <c r="D68" s="100"/>
+      <c r="E68" s="100"/>
+      <c r="F68" s="100"/>
+      <c r="G68" s="100"/>
+      <c r="H68" s="100"/>
+      <c r="I68" s="100"/>
+      <c r="J68" s="101"/>
       <c r="M68" s="60"/>
-      <c r="N68" s="101" t="s">
+      <c r="N68" s="102" t="s">
         <v>302</v>
       </c>
-      <c r="O68" s="101"/>
-      <c r="P68" s="101"/>
-      <c r="Q68" s="101"/>
-      <c r="R68" s="101"/>
-      <c r="S68" s="101"/>
-      <c r="T68" s="101"/>
-      <c r="U68" s="102"/>
+      <c r="O68" s="102"/>
+      <c r="P68" s="102"/>
+      <c r="Q68" s="102"/>
+      <c r="R68" s="102"/>
+      <c r="S68" s="102"/>
+      <c r="T68" s="102"/>
+      <c r="U68" s="103"/>
     </row>
     <row r="69" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B69" s="103" t="s">
+      <c r="B69" s="104" t="s">
         <v>253</v>
       </c>
       <c r="C69" s="61">
         <f ca="1">+J4</f>
-        <v>150.73682790166654</v>
+        <v>149.81272597413047</v>
       </c>
       <c r="D69" s="62">
         <v>0.01</v>
@@ -29946,12 +29946,12 @@
       <c r="J69" s="62">
         <v>0.04</v>
       </c>
-      <c r="M69" s="103" t="s">
+      <c r="M69" s="104" t="s">
         <v>253</v>
       </c>
       <c r="N69" s="61">
         <f ca="1">+J4</f>
-        <v>150.73682790166654</v>
+        <v>149.81272597413047</v>
       </c>
       <c r="O69" s="62">
         <v>7.0000000000000007E-2</v>
@@ -29976,369 +29976,369 @@
       </c>
     </row>
     <row r="70" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B70" s="103"/>
+      <c r="B70" s="104"/>
       <c r="C70" s="63">
         <v>0.05</v>
       </c>
       <c r="D70" s="64">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>394.46547141114547</v>
+        <v>392.93647361299662</v>
       </c>
       <c r="E70" s="64">
-        <v>423.22127284207443</v>
+        <v>421.37447195342565</v>
       </c>
       <c r="F70" s="64">
-        <v>461.38317754480266</v>
+        <v>459.11461928371483</v>
       </c>
       <c r="G70" s="65">
-        <v>514.59484748240959</v>
+        <v>511.73820499777975</v>
       </c>
       <c r="H70" s="64">
-        <v>594.14360658105431</v>
+        <v>590.40780788345285</v>
       </c>
       <c r="I70" s="64">
-        <v>726.36654400177463</v>
+        <v>721.16944511234169</v>
       </c>
       <c r="J70" s="64">
-        <v>990.27492722768329</v>
-      </c>
-      <c r="M70" s="103"/>
+        <v>982.16116819926992</v>
+      </c>
+      <c r="M70" s="104"/>
       <c r="N70" s="63">
         <v>0.05</v>
       </c>
       <c r="O70" s="64">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>435.89071806531416</v>
+        <v>433.9038971234412</v>
       </c>
       <c r="P70" s="64">
-        <v>459.50195689044284</v>
+        <v>457.25418948574281</v>
       </c>
       <c r="Q70" s="64">
-        <v>477.86625375443174</v>
+        <v>475.41552798975511</v>
       </c>
       <c r="R70" s="65">
-        <v>492.55769124562283</v>
+        <v>489.94459879296494</v>
       </c>
       <c r="S70" s="64">
-        <v>504.5779582838702</v>
+        <v>501.83202035922761</v>
       </c>
       <c r="T70" s="64">
-        <v>514.59484748240959</v>
+        <v>511.73820499777975</v>
       </c>
       <c r="U70" s="64">
-        <v>523.07067680425064</v>
+        <v>520.12036123040093</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B71" s="103"/>
+      <c r="B71" s="104"/>
       <c r="C71" s="63">
         <v>0.06</v>
       </c>
       <c r="D71" s="64">
-        <v>308.95037477597037</v>
+        <v>307.63927864815759</v>
       </c>
       <c r="E71" s="64">
-        <v>323.34870851193108</v>
+        <v>321.8477750623324</v>
       </c>
       <c r="F71" s="64">
-        <v>341.22363308163159</v>
+        <v>339.48702459701411</v>
       </c>
       <c r="G71" s="65">
-        <v>364.06511598524634</v>
+        <v>362.02735001813426</v>
       </c>
       <c r="H71" s="64">
-        <v>394.35643638973238</v>
+        <v>391.919289268912</v>
       </c>
       <c r="I71" s="64">
-        <v>436.56749679561239</v>
+        <v>433.57381064714195</v>
       </c>
       <c r="J71" s="64">
-        <v>499.63810220393191</v>
-      </c>
-      <c r="M71" s="103"/>
+        <v>495.81285074841338</v>
+      </c>
+      <c r="M71" s="104"/>
       <c r="N71" s="63">
         <v>0.06</v>
       </c>
       <c r="O71" s="64">
-        <v>312.60902812545493</v>
+        <v>311.24969384967682</v>
       </c>
       <c r="P71" s="64">
-        <v>328.04585448339236</v>
+        <v>326.48299070021403</v>
       </c>
       <c r="Q71" s="64">
-        <v>340.05227498401035</v>
+        <v>338.33111047285411</v>
       </c>
       <c r="R71" s="65">
-        <v>349.65741138450471</v>
+        <v>347.80960629096609</v>
       </c>
       <c r="S71" s="64">
-        <v>357.51615934854556</v>
+        <v>355.56473923305782</v>
       </c>
       <c r="T71" s="64">
-        <v>364.06511598524634</v>
+        <v>362.02735001813426</v>
       </c>
       <c r="U71" s="64">
-        <v>369.60654083168538</v>
+        <v>367.49571299012194</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B72" s="103"/>
+      <c r="B72" s="104"/>
       <c r="C72" s="63">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D72" s="65">
-        <v>252.02733057711799</v>
+        <v>250.86799113361616</v>
       </c>
       <c r="E72" s="65">
-        <v>259.78446874346179</v>
+        <v>258.50649944245151</v>
       </c>
       <c r="F72" s="65">
-        <v>269.00289878269075</v>
+        <v>267.58395209819787</v>
       </c>
       <c r="G72" s="65">
-        <v>280.16971798576662</v>
+        <v>278.57999721649202</v>
       </c>
       <c r="H72" s="65">
-        <v>294.01557228913208</v>
+        <v>292.2141069707896</v>
       </c>
       <c r="I72" s="65">
-        <v>311.68861959291104</v>
+        <v>309.61688049080612</v>
       </c>
       <c r="J72" s="65">
-        <v>335.10245639731045</v>
-      </c>
-      <c r="M72" s="103"/>
+        <v>332.6726496594012</v>
+      </c>
+      <c r="M72" s="104"/>
       <c r="N72" s="63">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O72" s="65">
-        <v>243.50735513133745</v>
+        <v>242.47831161030516</v>
       </c>
       <c r="P72" s="65">
-        <v>254.50606398766621</v>
+        <v>253.30881729216125</v>
       </c>
       <c r="Q72" s="65">
-        <v>263.06061532036637</v>
+        <v>261.73254393360486</v>
       </c>
       <c r="R72" s="65">
-        <v>269.90425638652647</v>
+        <v>268.47152524675977</v>
       </c>
       <c r="S72" s="65">
-        <v>275.50359907702114</v>
+        <v>273.98523723025011</v>
       </c>
       <c r="T72" s="65">
-        <v>280.16971798576662</v>
+        <v>278.57999721649202</v>
       </c>
       <c r="U72" s="65">
-        <v>284.11797244701285</v>
+        <v>282.46787105100452</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B73" s="103"/>
+      <c r="B73" s="104"/>
       <c r="C73" s="63">
         <v>0.09</v>
       </c>
       <c r="D73" s="64">
-        <v>181.05255156558508</v>
+        <v>180.09581068551762</v>
       </c>
       <c r="E73" s="64">
-        <v>183.49789079906833</v>
+        <v>182.49361750647282</v>
       </c>
       <c r="F73" s="64">
-        <v>186.23840387136627</v>
+        <v>185.18086058820774</v>
       </c>
       <c r="G73" s="65">
-        <v>189.34220782220532</v>
+        <v>188.22433291397925</v>
       </c>
       <c r="H73" s="64">
-        <v>192.90012537122089</v>
+        <v>191.71309179479661</v>
       </c>
       <c r="I73" s="64">
-        <v>197.03600568155193</v>
+        <v>195.76857901839941</v>
       </c>
       <c r="J73" s="64">
-        <v>201.92323758159313</v>
-      </c>
-      <c r="M73" s="103"/>
+        <v>200.56081308762342</v>
+      </c>
+      <c r="M73" s="104"/>
       <c r="N73" s="63">
         <v>0.09</v>
       </c>
       <c r="O73" s="64">
-        <v>167.99053634831225</v>
+        <v>167.28769443132268</v>
       </c>
       <c r="P73" s="64">
-        <v>174.39603779048016</v>
+        <v>173.5686859761197</v>
       </c>
       <c r="Q73" s="64">
-        <v>179.37809446772189</v>
+        <v>178.45390162207286</v>
       </c>
       <c r="R73" s="65">
-        <v>183.36373980951527</v>
+        <v>182.3620741388354</v>
       </c>
       <c r="S73" s="64">
-        <v>186.62472236189166</v>
+        <v>185.55966983436841</v>
       </c>
       <c r="T73" s="64">
-        <v>189.34220782220532</v>
+        <v>188.22433291397925</v>
       </c>
       <c r="U73" s="64">
-        <v>191.64161859631687</v>
+        <v>190.47904782749612</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B74" s="103"/>
+      <c r="B74" s="104"/>
       <c r="C74" s="63">
         <v>0.1</v>
       </c>
       <c r="D74" s="64">
-        <v>157.46710934115134</v>
+        <v>156.5829683699568</v>
       </c>
       <c r="E74" s="64">
-        <v>158.8164260525773</v>
+        <v>157.90330771571476</v>
       </c>
       <c r="F74" s="64">
-        <v>160.29089018243229</v>
+        <v>159.34610686588533</v>
       </c>
       <c r="G74" s="65">
-        <v>161.91553121440219</v>
+        <v>160.93585778135107</v>
       </c>
       <c r="H74" s="64">
-        <v>163.72252991322583</v>
+        <v>162.70405012610379</v>
       </c>
       <c r="I74" s="64">
-        <v>165.75396881740795</v>
+        <v>164.69186269151734</v>
       </c>
       <c r="J74" s="64">
-        <v>168.06595797828817</v>
-      </c>
-      <c r="M74" s="103"/>
+        <v>166.95420053275703</v>
+      </c>
+      <c r="M74" s="104"/>
       <c r="N74" s="63">
         <v>0.1</v>
       </c>
       <c r="O74" s="64">
-        <v>144.92311225757439</v>
+        <v>144.30836096142889</v>
       </c>
       <c r="P74" s="64">
-        <v>150.02083794462274</v>
+        <v>149.29661000740555</v>
       </c>
       <c r="Q74" s="64">
-        <v>153.98573570121587</v>
+        <v>153.17635926538739</v>
       </c>
       <c r="R74" s="65">
-        <v>157.1576539064904</v>
+        <v>156.28015867177285</v>
       </c>
       <c r="S74" s="64">
-        <v>159.75285971080589</v>
+        <v>158.81963091336095</v>
       </c>
       <c r="T74" s="64">
-        <v>161.91553121440219</v>
+        <v>160.93585778135107</v>
       </c>
       <c r="U74" s="64">
-        <v>163.74548402513747</v>
+        <v>162.72651128503497</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B75" s="103"/>
+      <c r="B75" s="104"/>
       <c r="C75" s="63">
         <v>0.11</v>
       </c>
       <c r="D75" s="64">
-        <v>138.63877541948526</v>
+        <v>137.81539999833475</v>
       </c>
       <c r="E75" s="64">
-        <v>139.33252158180125</v>
+        <v>138.49284965390351</v>
       </c>
       <c r="F75" s="64">
-        <v>140.06780270852775</v>
+        <v>139.21085859305811</v>
       </c>
       <c r="G75" s="65">
-        <v>140.8519484992666</v>
+        <v>139.9765843364313</v>
       </c>
       <c r="H75" s="64">
-        <v>141.69412107852017</v>
+        <v>140.79897378481417</v>
       </c>
       <c r="I75" s="64">
-        <v>142.60592580399128</v>
+        <v>141.68935967920851</v>
       </c>
       <c r="J75" s="64">
-        <v>143.60228384986959</v>
-      </c>
-      <c r="M75" s="103"/>
+        <v>142.66231268661684</v>
+      </c>
+      <c r="M75" s="104"/>
       <c r="N75" s="63">
         <v>0.11</v>
       </c>
       <c r="O75" s="64">
-        <v>127.07338674771225</v>
+        <v>126.52168913144497</v>
       </c>
       <c r="P75" s="64">
-        <v>131.20695527317858</v>
+        <v>130.55815769294088</v>
       </c>
       <c r="Q75" s="64">
-        <v>134.42195301520792</v>
+        <v>133.69763324077104</v>
       </c>
       <c r="R75" s="65">
-        <v>136.99395120883142</v>
+        <v>136.20921367903514</v>
       </c>
       <c r="S75" s="64">
-        <v>139.0983133672506</v>
+        <v>138.26414312852395</v>
       </c>
       <c r="T75" s="64">
-        <v>140.8519484992666</v>
+        <v>139.9765843364313</v>
       </c>
       <c r="U75" s="64">
-        <v>142.33579361097247</v>
+        <v>141.42557305081445</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
-      <c r="B76" s="104"/>
+      <c r="B76" s="105"/>
       <c r="C76" s="63">
         <v>0.12</v>
       </c>
       <c r="D76" s="64">
-        <v>123.26788652234154</v>
+        <v>122.49645561593972</v>
       </c>
       <c r="E76" s="64">
-        <v>123.56212022441525</v>
+        <v>122.78319123420344</v>
       </c>
       <c r="F76" s="64">
-        <v>123.85635392648895</v>
+        <v>123.06992685246716</v>
       </c>
       <c r="G76" s="65">
-        <v>124.15058762856263</v>
+        <v>123.35666247073084</v>
       </c>
       <c r="H76" s="64">
-        <v>124.44482133063636</v>
+        <v>123.64339808899457</v>
       </c>
       <c r="I76" s="64">
-        <v>124.73905503271004</v>
+        <v>123.93013370725828</v>
       </c>
       <c r="J76" s="64">
-        <v>125.03328873478377</v>
-      </c>
-      <c r="M76" s="104"/>
+        <v>124.21686932552198</v>
+      </c>
+      <c r="M76" s="105"/>
       <c r="N76" s="63">
         <v>0.12</v>
       </c>
       <c r="O76" s="64">
-        <v>112.81263482309103</v>
+        <v>112.30763958650907</v>
       </c>
       <c r="P76" s="64">
-        <v>116.21402066473252</v>
+        <v>115.6223464517756</v>
       </c>
       <c r="Q76" s="64">
-        <v>118.85954298600923</v>
+        <v>118.20045179142734</v>
       </c>
       <c r="R76" s="65">
-        <v>120.97596084303059</v>
+        <v>120.26293606314876</v>
       </c>
       <c r="S76" s="64">
-        <v>122.70757545332081</v>
+        <v>121.95042319455715</v>
       </c>
       <c r="T76" s="64">
-        <v>124.15058762856263</v>
+        <v>123.35666247073084</v>
       </c>
       <c r="U76" s="64">
-        <v>125.37159793069037</v>
+        <v>124.54655724287781</v>
       </c>
     </row>
   </sheetData>
